--- a/artfynd/A 9724-2022 artfynd.xlsx
+++ b/artfynd/A 9724-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9724-2022 artfynd.xlsx
+++ b/artfynd/A 9724-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3169,32 +3169,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>99108709</v>
+        <v>99108867</v>
       </c>
       <c r="B21" t="n">
-        <v>56990</v>
+        <v>56401</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dialog hos validator</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102125</v>
+        <v>100048</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3208,11 +3208,7 @@
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -3229,13 +3225,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>800443.269283338</v>
+        <v>800543.3332374105</v>
       </c>
       <c r="R21" t="n">
-        <v>7272784.683025718</v>
+        <v>7272786.236275285</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3279,7 +3275,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>i lämplig häckbiotop</t>
+          <t>lämplig häckningsbiotop, permanent revir, flera spår i barken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3298,7 +3294,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>äldre hänglavsrik skog</t>
+          <t>strukturrik, blandat boreal skog, med gamla och döda träd samt buskar</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3313,149 +3309,6 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>99108867</v>
-      </c>
-      <c r="B22" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Lappstugärdan, Harrträsket, Nb</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>800543.3332374105</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7272786.236275285</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Piteå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Norrfjärden</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2022-03-13</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2022-03-13</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>lämplig häckningsbiotop, permanent revir, flera spår i barken</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>strukturrik, blandat boreal skog, med gamla och döda träd samt buskar</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Corina Delling</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Corina Delling</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
